--- a/SHET/GZ001/gzotkl2.xlsx
+++ b/SHET/GZ001/gzotkl2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZ001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730E056C-534B-48B0-8A2F-3A3B125A923B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B06E60-5794-4CA1-A772-D68347270654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t>Название таблицы</t>
   </si>
@@ -52,18 +52,12 @@
     <t>ФК</t>
   </si>
   <si>
-    <t>ЖС</t>
-  </si>
-  <si>
     <t>X:161, X:221</t>
   </si>
   <si>
     <t>Срабатывание выходного реле при введеном SA1</t>
   </si>
   <si>
-    <t>Воздействие</t>
-  </si>
-  <si>
     <t>ГЗ АТ откл: Срабатывание</t>
   </si>
   <si>
@@ -104,6 +98,18 @@
   </si>
   <si>
     <t>**) - срабатывание после Tбл ГЗ АТ откл</t>
+  </si>
+  <si>
+    <t>Вход для проверки</t>
+  </si>
+  <si>
+    <t>Выход для контроля</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ТС</t>
   </si>
 </sst>
 </file>
@@ -142,11 +148,11 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,186 +434,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="1">
+      <c r="C2" s="2"/>
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2</v>
       </c>
-      <c r="E2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -627,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -635,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/SHET/GZ001/gzotkl2.xlsx
+++ b/SHET/GZ001/gzotkl2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZ001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B06E60-5794-4CA1-A772-D68347270654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE784CE-7918-4AA8-86EA-73EF5B00D68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>X:161, X:221</t>
   </si>
   <si>
-    <t>Срабатывание выходного реле при введеном SA1</t>
-  </si>
-  <si>
     <t>ГЗ АТ откл: Срабатывание</t>
   </si>
   <si>
@@ -110,6 +107,9 @@
   </si>
   <si>
     <t>ТС</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле</t>
   </si>
 </sst>
 </file>
@@ -447,13 +447,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -477,13 +477,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -497,13 +497,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -520,10 +520,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -537,16 +537,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
@@ -557,16 +557,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -577,16 +577,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -597,16 +597,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -627,7 +627,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -670,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
